--- a/sipii_caixa_20260527.xlsx
+++ b/sipii_caixa_20260527.xlsx
@@ -94,10 +94,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -628,7 +628,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,25079100</t>
+          <t>2,25184400</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>4,74</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>12,86</t>
+          <t>12,85</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>406,754</t>
+          <t>407,232</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,47068900</t>
+          <t>5,47319100</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>4,65</t>
+          <t>4,70</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.590,423</t>
+          <t>6.603,336</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,76225700</t>
+          <t>2,76352100</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>4,64</t>
+          <t>4,69</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>12,61</t>
+          <t>12,60</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>829,136</t>
+          <t>861,740</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -931,22 +931,22 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3,31289400</t>
+          <t>3,31460400</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>11,489</t>
+          <t>11,569</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -1000,22 +1000,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,46649000</t>
+          <t>3,46828400</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>120,255</t>
+          <t>120,005</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1117,32 +1117,32 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.824,50240700</t>
+          <t>1.825,48334600</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>5,28</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>14,67</t>
+          <t>14,66</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>96,475</t>
+          <t>97,079</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1234,22 +1234,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,65184500</t>
+          <t>9,65656300</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>4,97</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>585,353</t>
+          <t>584,983</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1351,22 +1351,22 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,33679400</t>
+          <t>3,33852800</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>5,24</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>61,272</t>
+          <t>61,284</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1468,32 +1468,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,97883300</t>
+          <t>2,98041100</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>5,40</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>14,84</t>
+          <t>14,83</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1.672,391</t>
+          <t>1.674,277</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1533,32 +1533,32 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>19,88931100</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>0,409</t>
+          <t>19,85273400</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>-0,183</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>3,76</t>
+          <t>3,57</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>12,32</t>
+          <t>12,01</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>123,550</t>
+          <t>123,270</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,49370500</t>
+          <t>13,49435700</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>0,160</t>
+          <t>0,004</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>10,00</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,449</t>
+          <t>28,433</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1767,32 +1767,32 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>45,90441200</t>
+          <t>45,92679000</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,80</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>4,91</t>
+          <t>4,96</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>13,35</t>
+          <t>13,34</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>40,677</t>
+          <t>40,697</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1884,22 +1884,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20,10582000</t>
+          <t>20,11546900</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>4,82</t>
+          <t>4,87</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,763</t>
+          <t>64,794</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3,14039100</t>
+          <t>3,14104800</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>0,141</t>
+          <t>0,020</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>5,73</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>11,11</t>
+          <t>11,17</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>79,826</t>
+          <t>79,845</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -2118,22 +2118,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14,87079700</t>
+          <t>14,87809500</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,968</t>
+          <t>27,942</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2,98367600</t>
+          <t>2,98509700</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>4,80</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>1,657</t>
+          <t>1,658</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -2352,32 +2352,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,31561300</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>0,387</t>
+          <t>3,31019800</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>-0,163</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>3,86</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>12,80</t>
+          <t>12,52</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>139,951</t>
+          <t>139,764</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2469,22 +2469,22 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,02119200</t>
+          <t>3,02282300</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>5,40</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.760,529</t>
+          <t>1.761,317</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2586,32 +2586,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32,60188400</t>
+          <t>32,61832600</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>13,83</t>
+          <t>13,82</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2.188,847</t>
+          <t>2.187,597</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2703,22 +2703,22 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,28663800</t>
+          <t>3,28829700</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>5,14</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>13,229</t>
+          <t>13,236</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2820,22 +2820,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3,33897500</t>
+          <t>3,34249700</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0,149</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
+          <t>0,105</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>0,11</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>4,88</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,838</t>
+          <t>66,983</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>18,92508400</t>
+          <t>18,93477900</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>5,20</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>958,155</t>
+          <t>958,430</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -3002,22 +3002,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,10981982</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
+          <t>1,11182293</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>-0,01</t>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2,88</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>210,334</t>
+          <t>212,497</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3119,22 +3119,22 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1,23272700</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
+          <t>1,23340200</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>70,786</t>
+          <t>70,866</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -3236,32 +3236,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1.820,75933100</t>
+          <t>1.821,75907000</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>5,42</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>14,82</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>175,373</t>
+          <t>175,323</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3305,32 +3305,32 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,19693800</t>
+          <t>1,19801900</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,090</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>6,50</t>
+          <t>6,60</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>12,82</t>
+          <t>12,96</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>40,203</t>
+          <t>40,239</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -3422,22 +3422,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,03303600</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,000</t>
+          <t>1,03359700</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>5,35</t>
+          <t>5,41</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,839</t>
+          <t>21,851</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3535,32 +3535,32 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,16099200</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>0,000</t>
+          <t>1,16170700</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>13,84</t>
+          <t>13,85</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>66,519</t>
+          <t>66,562</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,06193675</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
+          <t>1,06332986</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2,77</t>
+          <t>2,90</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>321,125</t>
+          <t>319,464</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3874,32 +3874,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5,10959100</t>
+          <t>5,11230800</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>14,85</t>
+          <t>14,84</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>861,741</t>
+          <t>860,938</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>4,91618500</t>
+          <t>4,91884200</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.246,101</t>
+          <t>3.247,276</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>29,09497800</t>
+          <t>29,10902400</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -4118,12 +4118,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>4,91</t>
+          <t>4,96</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,240</t>
+          <t>21,251</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4225,22 +4225,22 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>30,43797500</t>
+          <t>30,45387500</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>5,30</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>3.114,179</t>
+          <t>3.116,203</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -4342,32 +4342,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1.765,93907400</t>
+          <t>1.766,25761100</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,096</t>
+          <t>0,018</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>4,83</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>13,70</t>
+          <t>13,64</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>125,911</t>
+          <t>125,896</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4459,22 +4459,22 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>3,20410400</t>
+          <t>3,20583400</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>578,670</t>
+          <t>581,881</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -4576,32 +4576,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>6,15416300</t>
+          <t>6,15732400</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>14,24</t>
+          <t>14,23</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>122,530</t>
+          <t>122,585</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1,26176600</t>
+          <t>1,26246000</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>338,194</t>
+          <t>337,787</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -4810,22 +4810,22 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10,53391300</t>
+          <t>10,53949200</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>5,43</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.385,810</t>
+          <t>2.387,796</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4927,22 +4927,22 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>5,48572700</t>
+          <t>5,48875200</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>555,617</t>
+          <t>555,566</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -5044,32 +5044,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3,54716600</t>
+          <t>3,54911200</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>15,01</t>
+          <t>15,00</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15.528,207</t>
+          <t>15.556,492</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5161,32 +5161,32 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>5,27239100</t>
+          <t>5,27513100</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0,060</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>15,23</t>
+          <t>15,22</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>1.388,431</t>
+          <t>1.388,284</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>30,17881300</t>
+          <t>30,19351400</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>4,88</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>166,020</t>
+          <t>165,888</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2,79472600</t>
+          <t>2,79605200</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>4,81</t>
+          <t>4,86</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5.917,642</t>
+          <t>5.919,794</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5625,22 +5625,22 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>3,58503100</t>
+          <t>3,58689400</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2.189,075</t>
+          <t>2.188,811</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -5742,22 +5742,22 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1,28344200</t>
+          <t>1,28413400</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>5,41</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>65,202</t>
+          <t>65,209</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>9,63105600</t>
+          <t>9,63609500</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>838,646</t>
+          <t>838,876</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>4,43212700</t>
+          <t>4,43449200</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>5,35</t>
+          <t>5,40</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15.735,976</t>
+          <t>15.784,652</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>4,74719600</t>
+          <t>4,74973600</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>5,41</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>9.455,265</t>
+          <t>9.431,611</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>5,07270700</t>
+          <t>5,07543200</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -6220,22 +6220,22 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>14,84</t>
+          <t>14,83</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>20.991,279</t>
+          <t>21.035,911</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>3,16828400</t>
+          <t>3,16999900</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -6289,22 +6289,22 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>14,96</t>
+          <t>14,95</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>13.351,574</t>
+          <t>13.325,941</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1.720,63337200</t>
+          <t>1.721,51500400</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>248,106</t>
+          <t>247,691</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6465,32 +6465,32 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1,40585300</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>0,000</t>
+          <t>1,40566100</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>-0,080</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>5,00</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>14,28</t>
+          <t>14,20</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>68,281</t>
+          <t>68,272</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.188,55802500</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
+          <t>1.187,95469000</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>-0,003</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>3,40</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>-5,27</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>0,21</t>
+          <t>3,35</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>-5,32</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>36,424</t>
+          <t>36,405</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6699,27 +6699,27 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>12,65058600</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>0,365</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>-0,70</t>
+          <t>12,62034000</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>-0,239</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>6,57</t>
+          <t>6,31</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>18,08</t>
+          <t>17,63</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -6768,32 +6768,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1.635,49048400</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>-0,006</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>-0,01</t>
+          <t>1.637,55822600</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>-0,163</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>0,10</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>4,37</t>
+          <t>4,50</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>13,27</t>
+          <t>13,26</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>116,929</t>
+          <t>115,457</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6885,32 +6885,32 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>2.427,83792800</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>0,152</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>0,12</t>
+          <t>2.422,49728200</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>-0,219</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>18,19</t>
+          <t>17,93</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>37,69</t>
+          <t>37,71</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>13,570</t>
+          <t>13,405</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -7115,32 +7115,32 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1,24900300</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>-0,005</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>-0,53</t>
+          <t>1,24854500</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>-0,332</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>10,84</t>
+          <t>10,72</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>6,407</t>
+          <t>6,410</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -7232,32 +7232,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,15806600</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>1,452</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>-4,29</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>-0,12</t>
+          <t>1,14894900</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>-0,787</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>-5,05</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>-0,90</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>16,72</t>
+          <t>15,21</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,508</t>
+          <t>3,481</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1,41975100</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>-0,004</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>-3,33</t>
+          <t>1,41938200</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>-0,729</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>-3,35</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>3,97</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>18,88</t>
+          <t>18,35</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>11,810</t>
+          <t>11,807</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7692,32 +7692,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1,10245300</t>
+          <t>1,10437600</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>0,193</t>
+          <t>0,174</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>-8,56</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>-7,43</t>
+          <t>0,61</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>-8,40</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>-7,75</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>3,702</t>
+          <t>3,738</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7809,32 +7809,32 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>5,33291181</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>5,33930383</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>-0,121</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>4,05</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>13,02</t>
+          <t>13,04</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>33,078</t>
+          <t>33,106</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -7926,32 +7926,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4,72104000</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>0,053</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>-1,47</t>
+          <t>4,69555700</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>-0,539</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>-2,00</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>5,67</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>41,55</t>
+          <t>40,77</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>639,349</t>
+          <t>632,603</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8043,32 +8043,32 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2,84761300</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>0,000</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>-0,18</t>
+          <t>2,84704900</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>-0,401</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>-0,20</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>10,43</t>
+          <t>10,30</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>76,636</t>
+          <t>76,621</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -8160,32 +8160,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1.651,42905900</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>-0,458</t>
+          <t>1.656,65385700</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>0,316</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>4,82</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>10,90</t>
+          <t>11,23</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>29,267</t>
+          <t>29,357</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8277,32 +8277,32 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>3,79859100</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>0,814</t>
+          <t>3,79340800</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>-0,136</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>4,97</t>
+          <t>4,83</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>12,92</t>
+          <t>12,76</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>41,56</t>
+          <t>39,74</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2.377,622</t>
+          <t>2.374,711</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -8394,32 +8394,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1,90203900</t>
+          <t>1,90226100</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>0,096</t>
+          <t>0,011</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>0,80</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>4,63</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>13,07</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>21,987</t>
+          <t>21,922</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1.656,37276600</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>1.658,55978400</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>-0,158</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>4,87</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>14,845</t>
+          <t>14,836</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -8624,22 +8624,22 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>0,53565193</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>-0,006</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>-1,26</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>-25,81</t>
+          <t>0,55118618</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>0,000</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>1,60</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>-23,66</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>3,926</t>
+          <t>4,039</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8741,32 +8741,32 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>3,26250100</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>-0,005</t>
+          <t>3,25686300</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>-0,541</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>1,39</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>2,39</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>8,41</t>
+          <t>8,06</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>155,456</t>
+          <t>155,188</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -8858,32 +8858,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1,54371700</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>-0,004</t>
+          <t>1,54597100</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>-0,198</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>3,38</t>
+          <t>3,53</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>20,32</t>
+          <t>20,28</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>14,611</t>
+          <t>14,633</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8975,32 +8975,32 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1,38222400</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>-0,003</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>-1,10</t>
+          <t>1,38073200</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>-0,220</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>1,81</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>8,01</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>70,950</t>
+          <t>70,873</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -9092,32 +9092,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1,48472000</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>1,48741900</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>-0,061</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>2,55</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>15,53</t>
+          <t>15,55</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>192,600</t>
+          <t>192,950</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9209,12 +9209,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,77265100</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>-0,001</t>
+          <t>1,77271200</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -9224,17 +9224,17 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>9,45</t>
+          <t>9,37</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>176,190</t>
+          <t>176,087</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -9326,32 +9326,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>5,61269600</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>0,228</t>
+          <t>5,60811300</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>-0,081</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>14,90</t>
+          <t>14,70</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>903,547</t>
+          <t>902,645</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9443,32 +9443,32 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,64444400</t>
+          <t>3,64492300</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>0,098</t>
+          <t>0,013</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>13,48</t>
+          <t>13,42</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>752,359</t>
+          <t>751,725</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -9560,32 +9560,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>6,79311100</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>6,82039100</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>5,62</t>
+          <t>6,04</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>16,19</t>
+          <t>16,60</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>129,652</t>
+          <t>130,173</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9677,17 +9677,17 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1,41388200</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
+          <t>1,41382700</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>-0,003</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>279,675</t>
+          <t>279,703</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -9794,32 +9794,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,31680300</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
+          <t>1,32365200</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>1,10</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>13,317</t>
+          <t>13,386</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9911,32 +9911,32 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3,73560200</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>-0,051</t>
+          <t>3,74765400</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>0,322</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>1,39</t>
-        </is>
-      </c>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>-7,07</t>
-        </is>
-      </c>
-      <c r="H85" s="7" t="inlineStr">
-        <is>
-          <t>-7,12</t>
+          <t>1,71</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>-6,77</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>-7,14</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>96,385</t>
+          <t>96,673</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -10028,32 +10028,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>6,76577100</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>0,818</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>-5,40</t>
+          <t>6,73248300</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>-0,492</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>-5,86</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>6,67</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>22,36</t>
+          <t>21,39</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>347,505</t>
+          <t>345,724</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10145,32 +10145,32 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2,64365400</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>0,914</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>-4,97</t>
+          <t>2,62560600</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>-0,682</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>-5,62</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>9,87</t>
+          <t>9,12</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>27,82</t>
+          <t>26,67</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>13,751</t>
+          <t>13,655</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -10262,32 +10262,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1.980,77142200</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>2,265</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>-4,76</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>-0,21</t>
+          <t>1.958,07515100</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>-1,145</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>-5,85</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>-1,36</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>17,56</t>
+          <t>15,59</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>10,578</t>
+          <t>10,461</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10375,32 +10375,32 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>10,05486600</t>
+          <t>10,08273100</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>0,513</t>
+          <t>0,277</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>6,72</t>
+          <t>7,01</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>1,54</t>
+          <t>1,82</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>23,13</t>
+          <t>22,50</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>276,621</t>
+          <t>277,347</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -10492,32 +10492,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1,50729200</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>2,645</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>-1,54</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>-1,12</t>
+          <t>1,49314600</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>-0,938</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>-2,46</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>-2,05</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>457,536</t>
+          <t>453,224</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10609,32 +10609,32 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1,13695100</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>2,507</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>-2,31</t>
+          <t>1,13007300</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>-0,604</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>-1,55</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>-2,90</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>59,432</t>
+          <t>58,398</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1,75482400</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>1,686</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>-5,50</t>
+          <t>1,73881100</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>-0,912</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>-6,36</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>2,00</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>14,32</t>
+          <t>12,52</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2,187</t>
+          <t>2,168</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10843,32 +10843,32 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>4,70066300</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>-2,893</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>-10,98</t>
+          <t>4,71952900</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>0,401</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>-10,63</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>49,27</t>
+          <t>49,86</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>54,93</t>
+          <t>55,51</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>80,015</t>
+          <t>80,325</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -10960,32 +10960,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>8,86083200</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>0,910</t>
-        </is>
-      </c>
-      <c r="F94" s="6" t="inlineStr">
-        <is>
-          <t>-5,03</t>
+          <t>8,79993100</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>-0,687</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>-5,68</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>9,44</t>
+          <t>8,68</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>26,46</t>
+          <t>25,32</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>92,539</t>
+          <t>91,898</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -11077,32 +11077,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,28503400</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>0,128</t>
-        </is>
-      </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>-5,89</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>-0,15</t>
+          <t>1,30250700</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>-0,036</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>-4,61</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>1,19</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>10,16</t>
+          <t>11,11</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>291,056</t>
+          <t>295,008</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -11194,32 +11194,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1,89035900</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>3,832</t>
-        </is>
-      </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>-1,48</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>-0,58</t>
+          <t>1,88061600</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>-0,515</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>-1,99</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>21,61</t>
+          <t>20,59</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>116,746</t>
+          <t>116,098</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11311,32 +11311,32 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>2,97478000</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>0,513</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>-7,61</t>
+          <t>2,95071100</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>-0,809</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>-8,36</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>9,14</t>
+          <t>8,26</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>22,99</t>
+          <t>21,13</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>132,589</t>
+          <t>129,845</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -11428,32 +11428,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,92531400</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>2,258</t>
-        </is>
-      </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>-4,82</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>-0,63</t>
+          <t>1,90320000</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>-1,148</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>-5,91</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>-1,77</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>16,24</t>
+          <t>14,30</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>49,373</t>
+          <t>48,800</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11545,32 +11545,32 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>6,63129900</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>-2,403</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>-11,43</t>
+          <t>6,63721700</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>0,089</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>-11,35</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>41,38</t>
+          <t>41,50</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>49,74</t>
+          <t>50,35</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>123,773</t>
+          <t>123,858</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -11662,32 +11662,32 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1.357,58309200</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>3,368</t>
-        </is>
-      </c>
-      <c r="F100" s="6" t="inlineStr">
-        <is>
-          <t>-2,59</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>-0,68</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>-9,40</t>
+          <t>1.323,79335000</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>-2,488</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>-5,02</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>-3,16</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>-12,54</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>43,611</t>
+          <t>42,531</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>39,57798900</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>0,580</t>
+          <t>39,32906600</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>-0,628</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>2,18</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>14,56</t>
+          <t>13,84</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>62,67</t>
+          <t>62,59</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>676,472</t>
+          <t>672,381</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -11896,15 +11896,15 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2,67071100</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>0,798</t>
-        </is>
-      </c>
-      <c r="F102" s="6" t="inlineStr">
+          <t>2,67069400</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>0,000</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
         <is>
           <t>-0,76</t>
         </is>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>25,22</t>
+          <t>26,30</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>444,617</t>
+          <t>444,288</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -12013,32 +12013,32 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>4,89765200</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>1,272</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
-        <is>
-          <t>-4,74</t>
+          <t>4,87185200</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>-0,526</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>-5,24</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>9,13</t>
+          <t>8,55</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>28,10</t>
+          <t>27,14</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>23,674</t>
+          <t>23,550</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -12130,32 +12130,32 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1.545,88240200</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>2,617</t>
-        </is>
-      </c>
-      <c r="F104" s="6" t="inlineStr">
-        <is>
-          <t>-4,64</t>
+          <t>1.528,22261500</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>-1,142</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>-5,73</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>6,22</t>
+          <t>5,01</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>18,75</t>
+          <t>16,98</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>30,953</t>
+          <t>30,627</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -12247,32 +12247,32 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>1,98537900</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>1,871</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>-3,14</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>-2,41</t>
+          <t>1,96731800</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>-0,909</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>-4,02</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>-3,29</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>12,85</t>
+          <t>11,39</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>1,818</t>
+          <t>1,802</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -12364,32 +12364,32 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,97893600</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>0,593</t>
-        </is>
-      </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>-5,44</t>
+          <t>5,97257000</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>-0,106</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>-5,54</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>11,14</t>
+          <t>11,02</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>29,55</t>
+          <t>29,14</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>44,383</t>
+          <t>44,331</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -12481,32 +12481,32 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>2,26121000</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>1,475</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>-3,82</t>
+          <t>2,25158300</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>-0,425</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>-4,23</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>7,77</t>
+          <t>7,31</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>26,29</t>
+          <t>25,48</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>36,314</t>
+          <t>36,139</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -12598,32 +12598,32 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>43,59458200</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>-2,889</t>
-        </is>
-      </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>-10,98</t>
+          <t>43,76941000</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>0,401</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>-10,62</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>49,32</t>
+          <t>49,92</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>55,05</t>
+          <t>55,63</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>874,765</t>
+          <t>875,765</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -12715,32 +12715,32 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>0,88600300</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>1,648</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>-3,58</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>-7,95</t>
-        </is>
-      </c>
-      <c r="H109" s="7" t="inlineStr">
-        <is>
-          <t>-16,49</t>
+          <t>0,88182400</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>-0,471</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>-4,04</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>-8,39</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>-16,98</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>2,989</t>
+          <t>2,985</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -12832,32 +12832,32 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1,20712400</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>1,056</t>
+          <t>1,20364200</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>-0,288</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>-0,24</t>
+          <t>0,52</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>16,05</t>
+          <t>14,89</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>3,883</t>
+          <t>3,872</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -12949,15 +12949,15 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>1,31943400</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>0,797</t>
-        </is>
-      </c>
-      <c r="F111" s="7" t="inlineStr">
+          <t>1,31941700</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <t>-0,77</t>
         </is>
@@ -12969,12 +12969,12 @@
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>25,05</t>
+          <t>26,12</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>19,628</t>
+          <t>19,626</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -13066,32 +13066,32 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,84209900</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>0,753</t>
-        </is>
-      </c>
-      <c r="F112" s="6" t="inlineStr">
-        <is>
-          <t>-12,28</t>
+          <t>1,81287400</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>-1,586</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>-13,67</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>5,45</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>74,27</t>
+          <t>71,39</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>284,948</t>
+          <t>280,269</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -13183,32 +13183,32 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1.003,28812900</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="inlineStr">
+          <t>1.013,48075100</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
         <is>
           <t>-0,002</t>
         </is>
       </c>
-      <c r="F113" s="7" t="inlineStr">
-        <is>
-          <t>-6,23</t>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>-5,28</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>3,37</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>17,92</t>
+          <t>18,62</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>7,914</t>
+          <t>7,995</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -13300,32 +13300,32 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1.513,24247100</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>-0,002</t>
-        </is>
-      </c>
-      <c r="F114" s="6" t="inlineStr">
-        <is>
-          <t>-5,93</t>
+          <t>1.532,14438800</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>-0,005</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>-4,75</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>2,43</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>13,50</t>
+          <t>14,20</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>22,057</t>
+          <t>22,304</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -13417,32 +13417,32 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>173,42888064</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>0,891</t>
-        </is>
-      </c>
-      <c r="F115" s="7" t="inlineStr">
-        <is>
-          <t>-4,99</t>
+          <t>172,25114375</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>-0,679</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>-5,63</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>10,05</t>
+          <t>9,31</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>28,42</t>
+          <t>27,26</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>43,358</t>
+          <t>43,064</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -13486,32 +13486,32 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1,88280000</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>0,732</t>
-        </is>
-      </c>
-      <c r="F116" s="6" t="inlineStr">
-        <is>
-          <t>-12,25</t>
+          <t>1,85223500</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>-1,623</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>-13,67</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>7,23</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>74,62</t>
+          <t>71,67</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>5,118</t>
+          <t>5,067</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -13603,32 +13603,32 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1,83649100</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>0,738</t>
-        </is>
-      </c>
-      <c r="F117" s="7" t="inlineStr">
-        <is>
-          <t>-12,30</t>
+          <t>1,80646900</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>-1,634</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>-13,73</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>7,27</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>74,71</t>
+          <t>71,73</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>1.678,798</t>
+          <t>1.650,665</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -13720,32 +13720,32 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>48,49443000</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>-2,889</t>
-        </is>
-      </c>
-      <c r="F118" s="6" t="inlineStr">
-        <is>
-          <t>-10,96</t>
+          <t>48,69024100</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>0,403</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>-10,60</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>49,73</t>
+          <t>50,33</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>55,95</t>
+          <t>56,54</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>702,624</t>
+          <t>704,676</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -13837,32 +13837,32 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>43,84760800</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>0,583</t>
+          <t>43,57238600</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>-0,627</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>14,79</t>
+          <t>14,07</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>63,57</t>
+          <t>63,49</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>794,807</t>
+          <t>789,708</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -13954,32 +13954,32 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>16,93582400</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>1,997</t>
-        </is>
-      </c>
-      <c r="F120" s="6" t="inlineStr">
-        <is>
-          <t>-4,49</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t>0,41</t>
+          <t>16,72559700</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>-1,241</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>-5,68</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>18,96</t>
+          <t>16,83</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>117,313</t>
+          <t>115,678</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -14071,32 +14071,32 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>36,76458400</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>0,579</t>
+          <t>36,53390100</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>-0,627</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>14,57</t>
+          <t>13,85</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>62,41</t>
+          <t>62,33</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>12,008</t>
+          <t>11,932</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -14188,32 +14188,32 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>42,84825100</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>-2,895</t>
-        </is>
-      </c>
-      <c r="F122" s="6" t="inlineStr">
-        <is>
-          <t>-10,98</t>
+          <t>43,02007600</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>0,401</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>-10,62</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>49,45</t>
+          <t>50,05</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>55,22</t>
+          <t>55,81</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>608,346</t>
+          <t>610,366</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -14305,32 +14305,32 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>37,75409600</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>0,580</t>
+          <t>37,51676900</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>-0,628</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>2,18</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>14,57</t>
+          <t>13,85</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>62,69</t>
+          <t>62,61</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>475,790</t>
+          <t>472,667</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -14422,32 +14422,32 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>45,55881400</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>-2,893</t>
-        </is>
-      </c>
-      <c r="F124" s="6" t="inlineStr">
-        <is>
-          <t>-10,96</t>
+          <t>45,74194300</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>0,401</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>-10,60</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>49,60</t>
+          <t>50,21</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>55,58</t>
+          <t>56,16</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>699,500</t>
+          <t>702,242</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -14539,22 +14539,22 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>1,12074800</t>
+          <t>1,12127500</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>4,80</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>54,589</t>
+          <t>56,895</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1,35254800</t>
+          <t>1,35318700</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -14666,12 +14666,12 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>4,80</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>196,879</t>
+          <t>211,825</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -14725,22 +14725,22 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>5,86415600</t>
+          <t>5,86711500</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>5,18</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -14750,7 +14750,7 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>41,534</t>
+          <t>41,562</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>5,10345500</t>
+          <t>5,10616800</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -14852,12 +14852,12 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>5,35</t>
+          <t>5,40</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>789,556</t>
+          <t>789,976</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -14959,22 +14959,22 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>3,20625900</t>
+          <t>3,20791900</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>5,20</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>18,683</t>
+          <t>18,773</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -15076,32 +15076,32 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>23,73544000</t>
+          <t>23,74106200</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>0,144</t>
+          <t>0,023</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>6,01</t>
+          <t>6,04</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>11,88</t>
+          <t>11,94</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>94,927</t>
+          <t>94,949</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,26071800</t>
+          <t>3,26240600</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,30</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>7.574,843</t>
+          <t>7.637,655</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -15310,22 +15310,22 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1.878,47946900</t>
+          <t>1.879,50162300</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,057</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
@@ -15335,7 +15335,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>15.673,394</t>
+          <t>15.759,437</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -15427,32 +15427,32 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>4,86121500</t>
+          <t>4,86360500</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,058</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>14,76</t>
+          <t>14,75</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>3.054,848</t>
+          <t>3.076,217</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -15544,7 +15544,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1,54322678</t>
+          <t>1,54405187</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -15554,22 +15554,22 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>14,76</t>
+          <t>14,75</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>343,973</t>
+          <t>344,157</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>5,10489700</t>
+          <t>5,10764800</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -15671,12 +15671,12 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>5,50</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>284,541</t>
+          <t>284,694</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -15778,22 +15778,22 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>8,67860700</t>
+          <t>8,68284400</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,059</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>5,43</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>3.998,992</t>
+          <t>4.000,878</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -15895,32 +15895,32 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>17,85039900</t>
+          <t>17,85930100</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,058</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>14,82</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>4.799,062</t>
+          <t>4.782,367</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -16008,7 +16008,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>2,81534100</t>
+          <t>2,81669900</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
@@ -16018,12 +16018,12 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>4,89</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>13.255,768</t>
+          <t>13.329,076</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>4,41177100</t>
+          <t>4,41416800</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -16135,12 +16135,12 @@
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>5,46</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -16150,7 +16150,7 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>12.431,013</t>
+          <t>12.474,465</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1,36884100</t>
+          <t>1,36958700</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -16267,7 +16267,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.606,551</t>
+          <t>3.614,012</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -16359,7 +16359,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1.765,82859000</t>
+          <t>1.766,76082200</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -16369,12 +16369,12 @@
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>5,37</t>
+          <t>5,43</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -16384,7 +16384,7 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>1.436,339</t>
+          <t>1.434,795</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1,30400800</t>
+          <t>1,30457500</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -16486,12 +16486,12 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>4,43</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>33.526,892</t>
+          <t>33.961,548</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>9,37283700</t>
+          <t>9,37720500</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -16603,12 +16603,12 @@
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>4,71</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -16618,7 +16618,7 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>2.892,268</t>
+          <t>2.923,563</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>2,46842800</t>
+          <t>2,46957900</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>4,71</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>15.417,030</t>
+          <t>15.479,484</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -16779,22 +16779,22 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>2,59688100</t>
+          <t>2,59823600</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>0,057</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>5,50</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>9.357,276</t>
+          <t>9.358,639</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -16896,32 +16896,32 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>2,40650900</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>0,284</t>
+          <t>2,40387900</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>-0,109</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>4,49</t>
+          <t>4,37</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>13,00</t>
+          <t>12,84</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>3.786,467</t>
+          <t>3.792,962</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -17013,32 +17013,32 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>2,98599000</t>
+          <t>2,98613300</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>0,169</t>
+          <t>0,004</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>5,88</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>11,99</t>
+          <t>12,01</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>41,811</t>
+          <t>41,813</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -17130,32 +17130,32 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1.640,09930600</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="inlineStr">
-        <is>
-          <t>0,155</t>
+          <t>1.639,69168900</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>-0,024</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>4,50</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>11,66</t>
+          <t>11,63</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>460,074</t>
+          <t>459,960</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -17247,32 +17247,32 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,46243900</t>
+          <t>4,46394000</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>0,076</t>
+          <t>0,033</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,20</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>14,27</t>
+          <t>14,23</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>11.182,178</t>
+          <t>11.160,417</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -17364,32 +17364,32 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,81974000</t>
+          <t>3,82122300</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>0,149</t>
+          <t>0,038</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>6,11</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>12,26</t>
+          <t>12,35</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2.982,391</t>
+          <t>2.983,638</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -17433,32 +17433,32 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>3,63777700</t>
-        </is>
-      </c>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>0,390</t>
+          <t>3,63189400</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>-0,161</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>4,20</t>
+          <t>4,03</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>13,08</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>1.750,385</t>
+          <t>1.745,899</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -17550,32 +17550,32 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>5,15048600</t>
+          <t>5,15628600</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>0,142</t>
-        </is>
-      </c>
-      <c r="F152" s="6" t="inlineStr">
-        <is>
-          <t>-0,02</t>
+          <t>0,112</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>4,74</t>
+          <t>4,86</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>10,18</t>
+          <t>10,23</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2.576,322</t>
+          <t>2.583,526</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -17667,32 +17667,32 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>5,17831000</t>
+          <t>5,17971000</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>0,142</t>
+          <t>0,027</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>6,07</t>
+          <t>6,10</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>12,06</t>
+          <t>12,12</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>5.440,008</t>
+          <t>5.441,101</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
@@ -17784,32 +17784,32 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>4,73939400</t>
+          <t>4,74034200</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>0,150</t>
+          <t>0,020</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>5,00</t>
+          <t>5,02</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>13,33</t>
+          <t>13,28</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>515,409</t>
+          <t>514,732</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -17901,32 +17901,32 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>7,91884300</t>
+          <t>7,92259200</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>0,059</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>14,60</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>166,923</t>
+          <t>167,328</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -17970,32 +17970,32 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>3,45945900</t>
+          <t>3,46600700</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>0,147</t>
-        </is>
-      </c>
-      <c r="F156" s="6" t="inlineStr">
-        <is>
-          <t>-0,71</t>
+          <t>0,189</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>-0,52</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>3,69</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>8,75</t>
+          <t>8,81</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>819,463</t>
+          <t>821,013</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -18087,32 +18087,32 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>3,77730800</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>0,511</t>
+          <t>3,76837100</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>-0,236</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>3,87</t>
+          <t>3,62</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>12,63</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>723,304</t>
+          <t>721,422</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -18204,32 +18204,32 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>7,14652400</t>
+          <t>7,15013200</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>5,40</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>14,68</t>
+          <t>14,67</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>12.898,853</t>
+          <t>12.892,091</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -18321,7 +18321,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>7,46316300</t>
+          <t>7,46708200</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18331,12 +18331,12 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>5,40</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
@@ -18346,7 +18346,7 @@
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>5.203,714</t>
+          <t>5.207,598</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -18438,32 +18438,32 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1,44864300</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="inlineStr">
-        <is>
-          <t>0,324</t>
+          <t>1,44626700</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>-0,164</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>3,89</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>12,66</t>
+          <t>12,36</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>172,950</t>
+          <t>172,666</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -18555,22 +18555,22 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>3,12782900</t>
+          <t>3,12939800</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -18580,7 +18580,7 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>1.902,168</t>
+          <t>1.859,155</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -18672,32 +18672,32 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>6,69259400</t>
+          <t>6,69620200</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>5,51</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>14,86</t>
+          <t>14,85</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>24.463,157</t>
+          <t>24.442,916</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -18741,22 +18741,22 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>5,51998900</t>
+          <t>5,52594700</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>0,151</t>
+          <t>0,107</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
@@ -18766,7 +18766,7 @@
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>598,801</t>
+          <t>597,248</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
@@ -18975,32 +18975,32 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,98630400</t>
-        </is>
-      </c>
-      <c r="E165" s="5" t="inlineStr">
-        <is>
-          <t>0,920</t>
-        </is>
-      </c>
-      <c r="F165" s="7" t="inlineStr">
-        <is>
-          <t>-4,97</t>
+          <t>3,95902400</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>-0,684</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>-5,62</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>10,09</t>
+          <t>9,34</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>28,46</t>
+          <t>27,30</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>302,030</t>
+          <t>299,957</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -19092,32 +19092,32 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>3,66308900</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>0,886</t>
-        </is>
-      </c>
-      <c r="F166" s="6" t="inlineStr">
-        <is>
-          <t>-4,96</t>
+          <t>3,63815900</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>-0,680</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>-5,61</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>9,12</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>27,93</t>
+          <t>26,80</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>9,269</t>
+          <t>9,206</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -19209,32 +19209,32 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>11,26971613</t>
+          <t>11,30132976</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>0,516</t>
+          <t>0,280</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>7,08</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>2,12</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
-          <t>24,15</t>
+          <t>23,51</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>2.326,280</t>
+          <t>2.332,770</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -19326,32 +19326,32 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>2,05202900</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="inlineStr">
-        <is>
-          <t>0,979</t>
-        </is>
-      </c>
-      <c r="F168" s="6" t="inlineStr">
-        <is>
-          <t>-4,64</t>
+          <t>2,03740700</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>-0,712</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>-5,32</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>8,26</t>
+          <t>7,49</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>25,19</t>
+          <t>24,09</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>202,563</t>
+          <t>201,119</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -19443,32 +19443,32 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>2,06042500</t>
-        </is>
-      </c>
-      <c r="E169" s="5" t="inlineStr">
-        <is>
-          <t>2,260</t>
-        </is>
-      </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>-4,82</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="inlineStr">
-        <is>
-          <t>-0,61</t>
+          <t>2,03673200</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>-1,149</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>-5,91</t>
+        </is>
+      </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>-1,76</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
-          <t>16,85</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>779,987</t>
+          <t>771,017</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
@@ -19560,32 +19560,32 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>3,47809986</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr">
-        <is>
-          <t>0,962</t>
-        </is>
-      </c>
-      <c r="F170" s="6" t="inlineStr">
-        <is>
-          <t>-5,65</t>
+          <t>3,45793778</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>-0,579</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>-6,19</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>6,90</t>
+          <t>6,29</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>22,43</t>
+          <t>21,40</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>1.333,772</t>
+          <t>1.326,040</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -19673,32 +19673,32 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2,54729879</t>
-        </is>
-      </c>
-      <c r="E171" s="5" t="inlineStr">
-        <is>
-          <t>1,096</t>
-        </is>
-      </c>
-      <c r="F171" s="7" t="inlineStr">
-        <is>
-          <t>-6,22</t>
+          <t>2,52966840</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>-0,692</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>-6,87</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>7,77</t>
+          <t>7,02</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>24,66</t>
+          <t>23,47</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>788,442</t>
+          <t>782,985</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
@@ -19786,32 +19786,32 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>3,73459200</t>
+          <t>3,73559500</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>0,080</t>
+          <t>0,026</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>5,20</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>14,32</t>
+          <t>14,28</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>4.974,238</t>
+          <t>4.981,567</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
